--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.6155281280883</v>
+        <v>3.35002332081435</v>
       </c>
       <c r="D2" t="n">
-        <v>32.09344339330382</v>
+        <v>5.21518455141187</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6550151942428091</v>
+        <v>0.1064399690644564</v>
       </c>
       <c r="F2" t="n">
-        <v>1.693235020847549</v>
+        <v>0.2751506908877266</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.92555851657392</v>
+        <v>3.562903258943262</v>
       </c>
       <c r="D3" t="n">
-        <v>28.70697335160872</v>
+        <v>4.664883169636417</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6550151942428091</v>
+        <v>0.1064399690644564</v>
       </c>
       <c r="F3" t="n">
-        <v>1.693235020847549</v>
+        <v>0.2751506908877266</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
